--- a/results/2025-01-17-REFERENCE COUNTER/_annex_A_2026-06-23-suction-mode.xlsx
+++ b/results/2025-01-17-REFERENCE COUNTER/_annex_A_2026-06-23-suction-mode.xlsx
@@ -5,17 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mp\projects\PR0118 - ISO 11171 Calibrations\results\2025-01-17-REFERENCE COUNTER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\mp\projects\PR0118 - ISO 11171 Calibrations\results\2025-01-17-REFERENCE COUNTER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B44785C-FDA2-4158-8329-975AC563F8D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C53330-3AC1-4141-B454-C5B8A13EC2E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17745" xr2:uid="{953665B5-C50E-440F-B37B-B0E68037AD87}"/>
+    <workbookView xWindow="0" yWindow="225" windowWidth="28995" windowHeight="17745" xr2:uid="{953665B5-C50E-440F-B37B-B0E68037AD87}"/>
   </bookViews>
   <sheets>
     <sheet name="Annex A" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="88">
   <si>
     <t>Annex A Preliminary Check</t>
   </si>
@@ -257,6 +258,54 @@
   </si>
   <si>
     <t>100ml weight</t>
+  </si>
+  <si>
+    <t>Density</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>Error ml</t>
+  </si>
+  <si>
+    <t>Programmed</t>
+  </si>
+  <si>
+    <t>Weight delta</t>
+  </si>
+  <si>
+    <t>BRAKING</t>
+  </si>
+  <si>
+    <t>MODE</t>
+  </si>
+  <si>
+    <t>COAST</t>
+  </si>
+  <si>
+    <t>STDDEV</t>
+  </si>
+  <si>
+    <t>Suction mode repeatability - 0ml flush, 10ml sample volume repeated tests</t>
+  </si>
+  <si>
+    <t>Programmed ml</t>
+  </si>
+  <si>
+    <t>g/100ml</t>
+  </si>
+  <si>
+    <t>Volume ml</t>
+  </si>
+  <si>
+    <t>Weight delta g</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Applied further 0.46ml correction</t>
   </si>
 </sst>
 </file>
@@ -645,7 +694,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -746,11 +795,23 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="0" xfId="3" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -823,6 +884,3339 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>10ml</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-GB" baseline="0"/>
+              <a:t> Set Samples &amp; volume taken</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.22505555555555556"/>
+          <c:y val="4.939768290526695E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Annex A'!$K$58</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Volume ml</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Annex A'!$M$58:$V$58</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>8.0595964335992498</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.036133270764898</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.9657437822618498</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.9305490380103247</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.9188174565931497</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.9657437822618489</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.8718911309244506</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.9070858751759747</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7.9070858751759747</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.8601595495072747</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A44D-4482-A880-045C2878F176}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Annex A'!$K$59</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Programmed ml</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Annex A'!$M$59:$V$59</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A44D-4482-A880-045C2878F176}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1328052352"/>
+        <c:axId val="1328065312"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1328052352"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1328065312"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1328065312"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="10"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1328052352"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Samples 10ml - 100ml</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Annex A'!$K$82</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Volume</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Annex A'!$L$82:$V$82</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="1">
+                  <c:v>7.913165266106442</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.880485527544348</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>27.87114845938375</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>37.955182072829132</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>48.004201680672267</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>57.738095238095234</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>67.962184873949568</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>77.941176470588232</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>87.791783380018657</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>97.747432306255831</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-577E-4AD5-8278-044882024F26}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Annex A'!$K$83</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Programmed ml</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Annex A'!$L$83:$V$83</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-577E-4AD5-8278-044882024F26}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1931074976"/>
+        <c:axId val="1931084576"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1931074976"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1931084576"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1931084576"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1931074976"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Measured</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-GB" baseline="0"/>
+              <a:t> Volumetric Accuracy</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-GB"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Annex A'!$K$138</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Error ml</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Annex A'!$M$137:$V$137</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Annex A'!$M$138:$V$138</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>-7.9365079365079083E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-7.0028011204499307E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-6.3025210084038719E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-1.4005602240899861E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-5.8356676003739949E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-3.267973856209494E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-7.7030812324935027E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-8.6367880485539672E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.13071895424837976</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.10504201680672054</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0071-40F0-AAEA-F440EF584006}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="1931082656"/>
+        <c:axId val="1931093696"/>
+      </c:barChart>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Annex A'!$K$136</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Volume</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Annex A'!$M$137:$V$137</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Annex A'!$M$136:$V$136</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>9.9206349206349209</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19.99299719887955</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>29.936974789915961</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>39.9859943977591</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>49.94164332399626</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>59.967320261437905</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>69.922969187675065</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>79.91363211951446</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>89.86928104575162</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>99.894957983193279</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0071-40F0-AAEA-F440EF584006}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1931099456"/>
+        <c:axId val="1931088416"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1931099456"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB"/>
+                  <a:t>Programmed</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-GB" baseline="0"/>
+                  <a:t> ml</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1931088416"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1931088416"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB"/>
+                  <a:t>Measured ml</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1931099456"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1931093696"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+          <c:min val="-1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB"/>
+                  <a:t>Deviation</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-GB" baseline="0"/>
+                  <a:t> ml</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-GB"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-GB"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1931082656"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="1931082656"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1931093696"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1021,6 +4415,206 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>565897</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>39221</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>56029</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="TextBox 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20582E32-0563-C24D-FAF6-787106D5327E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10270191" y="7356662"/>
+          <a:ext cx="6079191" cy="1473573"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100"/>
+            <a:t>Measure</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t> weight decrease for various small set sample volumes to identify offset.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-GB" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>20ml/min = 0.333ml/s. 0.3s deadtime = 0.100ml.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t>Pump wind-up will likely contribute more. 1 rev ~ </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>792817</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>132790</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>423023</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>52106</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E7582F2-471A-DB7E-42B7-60AF101C01BD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>725069</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>91530</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>761998</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>24958</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{007E6AF9-9530-1CE0-4028-DDAAF119D25F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>686359</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>20729</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>316565</xdr:colOff>
+      <xdr:row>158</xdr:row>
+      <xdr:rowOff>1680</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18FB6575-70B5-53A0-F334-D639E087A3FD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1135,7 +4729,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14F374CC-0343-4F47-9FB7-E69C7E4F9095}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:W56"/>
+  <dimension ref="A1:Z138"/>
   <sheetFormatPr defaultColWidth="11.53125" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="15.19921875" customWidth="1"/>
@@ -1143,13 +4737,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="36.75" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -1461,7 +5055,7 @@
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="59">
+      <c r="D12" s="58">
         <v>10443</v>
       </c>
       <c r="E12" s="1"/>
@@ -1959,7 +5553,7 @@
       <c r="H32" s="11"/>
       <c r="I32" s="52"/>
     </row>
-    <row r="33" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1975,20 +5569,32 @@
       </c>
       <c r="I33" s="57"/>
     </row>
-    <row r="34" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="31"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
-    </row>
-    <row r="35" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="M34" t="s">
+        <v>79</v>
+      </c>
+      <c r="T34" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
-    </row>
-    <row r="36" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="M35" t="s">
+        <v>78</v>
+      </c>
+      <c r="T35" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -2001,8 +5607,47 @@
         <v>85.11</v>
       </c>
       <c r="I36" s="50"/>
-    </row>
-    <row r="37" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="K36" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="L36" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="M36" s="24">
+        <v>1</v>
+      </c>
+      <c r="N36">
+        <v>2</v>
+      </c>
+      <c r="O36">
+        <v>3</v>
+      </c>
+      <c r="P36" s="24">
+        <v>4</v>
+      </c>
+      <c r="Q36" s="24">
+        <v>5</v>
+      </c>
+      <c r="R36" s="24">
+        <v>6</v>
+      </c>
+      <c r="S36" s="24">
+        <v>7</v>
+      </c>
+      <c r="T36" s="24">
+        <v>8</v>
+      </c>
+      <c r="U36" s="24">
+        <v>9</v>
+      </c>
+      <c r="V36" s="24">
+        <v>10</v>
+      </c>
+      <c r="W36" s="24">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2017,8 +5662,52 @@
       <c r="I37" s="52" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" ht="15.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="K37" s="24">
+        <v>85.35</v>
+      </c>
+      <c r="L37" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="M37" s="28">
+        <v>7.14</v>
+      </c>
+      <c r="N37">
+        <v>7.08</v>
+      </c>
+      <c r="O37">
+        <v>7.08</v>
+      </c>
+      <c r="P37">
+        <v>18.53</v>
+      </c>
+      <c r="Q37">
+        <v>8.67</v>
+      </c>
+      <c r="R37">
+        <v>8.68</v>
+      </c>
+      <c r="S37">
+        <v>17.329999999999998</v>
+      </c>
+      <c r="T37">
+        <v>7</v>
+      </c>
+      <c r="U37">
+        <f>13.84-7</f>
+        <v>6.84</v>
+      </c>
+      <c r="V37">
+        <v>6.79</v>
+      </c>
+      <c r="W37">
+        <v>6.76</v>
+      </c>
+      <c r="X37">
+        <f>13.58-W37</f>
+        <v>6.82</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" ht="15.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="1"/>
       <c r="B38" s="1" t="s">
         <v>67</v>
@@ -2042,8 +5731,67 @@
         <v>11</v>
       </c>
       <c r="J38" s="44"/>
-    </row>
-    <row r="39" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="L38" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="M38" s="28">
+        <f t="shared" ref="M38:Z38" si="0">M37/$K37*100</f>
+        <v>8.3655536028119517</v>
+      </c>
+      <c r="N38" s="60">
+        <f t="shared" si="0"/>
+        <v>8.2952548330404223</v>
+      </c>
+      <c r="O38" s="60">
+        <f t="shared" si="0"/>
+        <v>8.2952548330404223</v>
+      </c>
+      <c r="P38" s="60">
+        <f t="shared" si="0"/>
+        <v>21.710603397773877</v>
+      </c>
+      <c r="Q38" s="60">
+        <f t="shared" si="0"/>
+        <v>10.15817223198594</v>
+      </c>
+      <c r="R38" s="60">
+        <f t="shared" si="0"/>
+        <v>10.16988869361453</v>
+      </c>
+      <c r="S38" s="60">
+        <f t="shared" si="0"/>
+        <v>20.304628002343293</v>
+      </c>
+      <c r="T38" s="60">
+        <f t="shared" si="0"/>
+        <v>8.2015231400117177</v>
+      </c>
+      <c r="U38" s="60">
+        <f t="shared" si="0"/>
+        <v>8.0140597539543066</v>
+      </c>
+      <c r="V38" s="60">
+        <f t="shared" si="0"/>
+        <v>7.9554774458113648</v>
+      </c>
+      <c r="W38" s="60">
+        <f t="shared" si="0"/>
+        <v>7.920328060925601</v>
+      </c>
+      <c r="X38" s="60">
+        <f t="shared" si="0"/>
+        <v>7.9906268306971295</v>
+      </c>
+      <c r="Y38" s="60">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Z38" s="60">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2060,8 +5808,53 @@
         <v>11</v>
       </c>
       <c r="J39" s="44"/>
-    </row>
-    <row r="40" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="L39" t="s">
+        <v>75</v>
+      </c>
+      <c r="M39">
+        <v>10</v>
+      </c>
+      <c r="N39">
+        <v>10</v>
+      </c>
+      <c r="O39">
+        <v>10</v>
+      </c>
+      <c r="P39">
+        <v>20</v>
+      </c>
+      <c r="Q39">
+        <v>10</v>
+      </c>
+      <c r="R39">
+        <v>10</v>
+      </c>
+      <c r="S39">
+        <v>20</v>
+      </c>
+      <c r="T39">
+        <v>10</v>
+      </c>
+      <c r="U39">
+        <v>10</v>
+      </c>
+      <c r="V39">
+        <v>10</v>
+      </c>
+      <c r="W39">
+        <v>10</v>
+      </c>
+      <c r="X39">
+        <v>10</v>
+      </c>
+      <c r="Y39">
+        <v>10</v>
+      </c>
+      <c r="Z39">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A40" s="6"/>
       <c r="F40" s="51" t="s">
         <v>63</v>
@@ -2074,8 +5867,67 @@
         <v>64</v>
       </c>
       <c r="J40" s="44"/>
-    </row>
-    <row r="41" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="L40" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="M40" s="28">
+        <f>M38-10</f>
+        <v>-1.6344463971880483</v>
+      </c>
+      <c r="N40" s="60">
+        <f>N38-10</f>
+        <v>-1.7047451669595777</v>
+      </c>
+      <c r="O40" s="60">
+        <f>O38-10</f>
+        <v>-1.7047451669595777</v>
+      </c>
+      <c r="P40" s="60">
+        <f>P38-P39</f>
+        <v>1.7106033977738768</v>
+      </c>
+      <c r="Q40" s="60">
+        <f>Q38-10</f>
+        <v>0.15817223198594021</v>
+      </c>
+      <c r="R40" s="60">
+        <f>R38-10</f>
+        <v>0.16988869361452963</v>
+      </c>
+      <c r="S40" s="60">
+        <f t="shared" ref="S40:Z40" si="1">S38-S39</f>
+        <v>0.30462800234329279</v>
+      </c>
+      <c r="T40" s="60">
+        <f t="shared" si="1"/>
+        <v>-1.7984768599882823</v>
+      </c>
+      <c r="U40" s="60">
+        <f t="shared" si="1"/>
+        <v>-1.9859402460456934</v>
+      </c>
+      <c r="V40" s="60">
+        <f t="shared" si="1"/>
+        <v>-2.0445225541886352</v>
+      </c>
+      <c r="W40" s="60">
+        <f t="shared" si="1"/>
+        <v>-2.079671939074399</v>
+      </c>
+      <c r="X40" s="60">
+        <f t="shared" si="1"/>
+        <v>-2.0093731693028705</v>
+      </c>
+      <c r="Y40" s="60">
+        <f t="shared" si="1"/>
+        <v>-10</v>
+      </c>
+      <c r="Z40" s="60">
+        <f t="shared" si="1"/>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B41" s="45"/>
       <c r="E41" s="1"/>
       <c r="F41" s="51" t="s">
@@ -2089,7 +5941,7 @@
       <c r="I41" s="52"/>
       <c r="J41" s="44"/>
     </row>
-    <row r="42" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
       <c r="E42" s="1"/>
       <c r="F42" s="53" t="s">
         <v>66</v>
@@ -2102,7 +5954,7 @@
       <c r="I42" s="52"/>
       <c r="J42" s="44"/>
     </row>
-    <row r="43" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
       <c r="E43" s="1"/>
       <c r="F43" s="51"/>
       <c r="G43" s="1"/>
@@ -2110,7 +5962,7 @@
       <c r="I43" s="52"/>
       <c r="J43" s="44"/>
     </row>
-    <row r="44" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
       <c r="C44" s="6"/>
       <c r="E44" s="46"/>
       <c r="F44" s="54" t="s">
@@ -2124,21 +5976,21 @@
       <c r="I44" s="57"/>
       <c r="J44" s="44"/>
     </row>
-    <row r="45" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="11"/>
       <c r="I45" s="1"/>
     </row>
-    <row r="46" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" s="11"/>
       <c r="I46" s="31"/>
     </row>
-    <row r="47" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
       <c r="E47" s="1"/>
       <c r="F47" s="47" t="s">
         <v>71</v>
@@ -2149,7 +6001,7 @@
       </c>
       <c r="I47" s="50"/>
     </row>
-    <row r="48" spans="1:10" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2166,7 +6018,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2183,7 +6035,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -2201,7 +6053,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
       <c r="F51" s="51" t="s">
         <v>63</v>
       </c>
@@ -2213,7 +6065,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
       <c r="F52" s="51" t="s">
         <v>65</v>
       </c>
@@ -2224,7 +6076,7 @@
       </c>
       <c r="I52" s="52"/>
     </row>
-    <row r="53" spans="1:9" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
       <c r="F53" s="53" t="s">
         <v>66</v>
       </c>
@@ -2234,14 +6086,23 @@
         <v>67.996289424860848</v>
       </c>
       <c r="I53" s="52"/>
-    </row>
-    <row r="54" spans="1:9" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="M53" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="54" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
       <c r="F54" s="51"/>
       <c r="G54" s="1"/>
       <c r="H54" s="11"/>
       <c r="I54" s="52"/>
-    </row>
-    <row r="55" spans="1:9" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="M54" t="s">
+        <v>78</v>
+      </c>
+      <c r="N54" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="55" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
       <c r="F55" s="54" t="s">
         <v>68</v>
       </c>
@@ -2251,11 +6112,1155 @@
         <v>-2.8624436787702212E-2</v>
       </c>
       <c r="I55" s="57"/>
-    </row>
-    <row r="56" spans="1:9" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="K55" s="63" t="s">
+        <v>72</v>
+      </c>
+      <c r="M55" s="21">
+        <v>85.24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
       <c r="H56" s="29"/>
+      <c r="K56" s="63" t="s">
+        <v>61</v>
+      </c>
+      <c r="M56" s="21">
+        <v>1</v>
+      </c>
+      <c r="N56" s="6">
+        <v>2</v>
+      </c>
+      <c r="O56" s="6">
+        <v>3</v>
+      </c>
+      <c r="P56" s="21">
+        <v>4</v>
+      </c>
+      <c r="Q56" s="21">
+        <v>5</v>
+      </c>
+      <c r="R56" s="21">
+        <v>6</v>
+      </c>
+      <c r="S56" s="21">
+        <v>7</v>
+      </c>
+      <c r="T56" s="21">
+        <v>8</v>
+      </c>
+      <c r="U56" s="21">
+        <v>9</v>
+      </c>
+      <c r="V56" s="21">
+        <v>10</v>
+      </c>
+      <c r="W56" s="24"/>
+    </row>
+    <row r="57" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="K57" s="63" t="s">
+        <v>85</v>
+      </c>
+      <c r="M57" s="28">
+        <v>6.87</v>
+      </c>
+      <c r="N57" s="61">
+        <v>6.85</v>
+      </c>
+      <c r="O57">
+        <v>6.79</v>
+      </c>
+      <c r="P57">
+        <v>6.76</v>
+      </c>
+      <c r="Q57">
+        <v>6.75</v>
+      </c>
+      <c r="R57">
+        <f>13.54-6.75</f>
+        <v>6.7899999999999991</v>
+      </c>
+      <c r="S57">
+        <f>20.25-13.54</f>
+        <v>6.7100000000000009</v>
+      </c>
+      <c r="T57">
+        <v>6.74</v>
+      </c>
+      <c r="U57">
+        <f>13.48-6.74</f>
+        <v>6.74</v>
+      </c>
+      <c r="V57">
+        <v>6.7</v>
+      </c>
+      <c r="Y57" s="60"/>
+      <c r="Z57" s="60"/>
+    </row>
+    <row r="58" spans="1:26" ht="13.9" x14ac:dyDescent="0.4">
+      <c r="F58" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="G58" s="48"/>
+      <c r="H58" s="49">
+        <v>85.35</v>
+      </c>
+      <c r="I58" s="50"/>
+      <c r="K58" s="63" t="s">
+        <v>84</v>
+      </c>
+      <c r="M58" s="13">
+        <f t="shared" ref="M58:V58" si="2">M57/$M55*100</f>
+        <v>8.0595964335992498</v>
+      </c>
+      <c r="N58" s="62">
+        <f t="shared" si="2"/>
+        <v>8.036133270764898</v>
+      </c>
+      <c r="O58" s="62">
+        <f t="shared" si="2"/>
+        <v>7.9657437822618498</v>
+      </c>
+      <c r="P58" s="62">
+        <f t="shared" si="2"/>
+        <v>7.9305490380103247</v>
+      </c>
+      <c r="Q58" s="62">
+        <f t="shared" si="2"/>
+        <v>7.9188174565931497</v>
+      </c>
+      <c r="R58" s="62">
+        <f t="shared" si="2"/>
+        <v>7.9657437822618489</v>
+      </c>
+      <c r="S58" s="62">
+        <f t="shared" si="2"/>
+        <v>7.8718911309244506</v>
+      </c>
+      <c r="T58" s="62">
+        <f t="shared" si="2"/>
+        <v>7.9070858751759747</v>
+      </c>
+      <c r="U58" s="62">
+        <f t="shared" si="2"/>
+        <v>7.9070858751759747</v>
+      </c>
+      <c r="V58" s="62">
+        <f t="shared" si="2"/>
+        <v>7.8601595495072747</v>
+      </c>
+      <c r="W58" s="61"/>
+      <c r="X58" s="61"/>
+    </row>
+    <row r="59" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="F59" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="G59" s="1"/>
+      <c r="H59" s="11">
+        <v>0</v>
+      </c>
+      <c r="I59" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K59" s="63" t="s">
+        <v>82</v>
+      </c>
+      <c r="M59">
+        <v>10</v>
+      </c>
+      <c r="N59">
+        <v>10</v>
+      </c>
+      <c r="O59">
+        <v>10</v>
+      </c>
+      <c r="P59">
+        <v>10</v>
+      </c>
+      <c r="Q59">
+        <v>10</v>
+      </c>
+      <c r="R59">
+        <v>10</v>
+      </c>
+      <c r="S59">
+        <v>10</v>
+      </c>
+      <c r="T59">
+        <v>10</v>
+      </c>
+      <c r="U59">
+        <v>10</v>
+      </c>
+      <c r="V59">
+        <v>10</v>
+      </c>
+      <c r="W59" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y59" s="60"/>
+      <c r="Z59" s="60"/>
+    </row>
+    <row r="60" spans="1:26" ht="13.9" x14ac:dyDescent="0.4">
+      <c r="F60" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="G60" s="1"/>
+      <c r="H60" s="11">
+        <v>10</v>
+      </c>
+      <c r="I60" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K60" s="63" t="s">
+        <v>74</v>
+      </c>
+      <c r="M60" s="13">
+        <f>M58-10</f>
+        <v>-1.9404035664007502</v>
+      </c>
+      <c r="N60" s="62">
+        <f>N58-10</f>
+        <v>-1.963866729235102</v>
+      </c>
+      <c r="O60" s="62">
+        <f>O58-10</f>
+        <v>-2.0342562177381502</v>
+      </c>
+      <c r="P60" s="62">
+        <f>P58-P59</f>
+        <v>-2.0694509619896753</v>
+      </c>
+      <c r="Q60" s="62">
+        <f>Q58-10</f>
+        <v>-2.0811825434068503</v>
+      </c>
+      <c r="R60" s="62">
+        <f>R58-10</f>
+        <v>-2.0342562177381511</v>
+      </c>
+      <c r="S60" s="62">
+        <f t="shared" ref="S60:V60" si="3">S58-S59</f>
+        <v>-2.1281088690755494</v>
+      </c>
+      <c r="T60" s="62">
+        <f t="shared" si="3"/>
+        <v>-2.0929141248240253</v>
+      </c>
+      <c r="U60" s="62">
+        <f t="shared" si="3"/>
+        <v>-2.0929141248240253</v>
+      </c>
+      <c r="V60" s="62">
+        <f t="shared" si="3"/>
+        <v>-2.1398404504927253</v>
+      </c>
+      <c r="W60" s="62">
+        <f>STDEV(M60:V60)</f>
+        <v>6.5435634798534967E-2</v>
+      </c>
+      <c r="X60" s="61" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="F61" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="G61" s="1"/>
+      <c r="H61" s="11">
+        <f>H59+H60</f>
+        <v>10</v>
+      </c>
+      <c r="I61" s="52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="F62" s="51" t="s">
+        <v>63</v>
+      </c>
+      <c r="G62" s="1"/>
+      <c r="H62" s="29">
+        <v>78.209999999999994</v>
+      </c>
+      <c r="I62" s="52" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="63" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="F63" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="G63" s="1"/>
+      <c r="H63" s="29">
+        <f>H58-H62</f>
+        <v>7.1400000000000006</v>
+      </c>
+      <c r="I63" s="52"/>
+    </row>
+    <row r="64" spans="1:26" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="F64" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="G64" s="42"/>
+      <c r="H64" s="43">
+        <f>H63/(H58/100)</f>
+        <v>8.3655536028119517</v>
+      </c>
+      <c r="I64" s="52"/>
+    </row>
+    <row r="65" spans="6:23" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="F65" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="G65" s="1"/>
+      <c r="H65" s="29">
+        <f>H64-H61</f>
+        <v>-1.6344463971880483</v>
+      </c>
+      <c r="I65" s="52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="6:23" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="F66" s="54" t="s">
+        <v>68</v>
+      </c>
+      <c r="G66" s="55"/>
+      <c r="H66" s="56">
+        <f>H64/H61-1</f>
+        <v>-0.16344463971880485</v>
+      </c>
+      <c r="I66" s="59"/>
+    </row>
+    <row r="69" spans="6:23" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="F69" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="G69" s="48"/>
+      <c r="H69" s="49">
+        <v>85.35</v>
+      </c>
+      <c r="I69" s="50"/>
+    </row>
+    <row r="70" spans="6:23" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="F70" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="G70" s="1"/>
+      <c r="H70" s="11">
+        <v>20</v>
+      </c>
+      <c r="I70" s="52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="6:23" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="F71" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="G71" s="1"/>
+      <c r="H71" s="11">
+        <v>50</v>
+      </c>
+      <c r="I71" s="52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="6:23" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="F72" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="G72" s="1"/>
+      <c r="H72" s="11">
+        <f>H70+H71</f>
+        <v>70</v>
+      </c>
+      <c r="I72" s="52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="6:23" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="F73" s="51" t="s">
+        <v>63</v>
+      </c>
+      <c r="G73" s="1"/>
+      <c r="H73" s="29">
+        <v>26.33</v>
+      </c>
+      <c r="I73" s="52" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="74" spans="6:23" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="F74" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="G74" s="1"/>
+      <c r="H74" s="29">
+        <f>H69-H73</f>
+        <v>59.019999999999996</v>
+      </c>
+      <c r="I74" s="52"/>
+    </row>
+    <row r="75" spans="6:23" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="F75" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="G75" s="42"/>
+      <c r="H75" s="43">
+        <f>H74/(H69/100)</f>
+        <v>69.150556531927364</v>
+      </c>
+      <c r="I75" s="52"/>
+    </row>
+    <row r="76" spans="6:23" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="F76" s="51"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="11"/>
+      <c r="I76" s="52"/>
+    </row>
+    <row r="77" spans="6:23" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="F77" s="54" t="s">
+        <v>68</v>
+      </c>
+      <c r="G77" s="55"/>
+      <c r="H77" s="56">
+        <f>H75/H72-1</f>
+        <v>-1.2134906686751989E-2</v>
+      </c>
+      <c r="I77" s="57"/>
+    </row>
+    <row r="78" spans="6:23" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="11"/>
+      <c r="I78" s="1"/>
+    </row>
+    <row r="79" spans="6:23" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="11"/>
+      <c r="I79" s="31"/>
+      <c r="K79" s="63" t="s">
+        <v>72</v>
+      </c>
+      <c r="L79" t="s">
+        <v>83</v>
+      </c>
+      <c r="M79" s="24">
+        <v>85.68</v>
+      </c>
+    </row>
+    <row r="80" spans="6:23" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="F80" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="G80" s="48"/>
+      <c r="H80" s="49"/>
+      <c r="I80" s="50"/>
+      <c r="K80" s="63" t="s">
+        <v>61</v>
+      </c>
+      <c r="M80" s="21">
+        <v>1</v>
+      </c>
+      <c r="N80" s="6">
+        <v>2</v>
+      </c>
+      <c r="O80" s="6">
+        <v>3</v>
+      </c>
+      <c r="P80" s="21">
+        <v>4</v>
+      </c>
+      <c r="Q80" s="21">
+        <v>5</v>
+      </c>
+      <c r="R80" s="21">
+        <v>6</v>
+      </c>
+      <c r="S80" s="21">
+        <v>7</v>
+      </c>
+      <c r="T80" s="21">
+        <v>8</v>
+      </c>
+      <c r="U80" s="21">
+        <v>9</v>
+      </c>
+      <c r="V80" s="21">
+        <v>10</v>
+      </c>
+      <c r="W80" s="24"/>
+    </row>
+    <row r="81" spans="6:24" ht="13.9" x14ac:dyDescent="0.4">
+      <c r="F81" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="G81" s="1"/>
+      <c r="H81" s="11">
+        <v>20</v>
+      </c>
+      <c r="I81" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K81" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="M81" s="64">
+        <v>6.78</v>
+      </c>
+      <c r="N81" s="65">
+        <v>15.32</v>
+      </c>
+      <c r="O81" s="66">
+        <v>23.88</v>
+      </c>
+      <c r="P81" s="66">
+        <v>32.520000000000003</v>
+      </c>
+      <c r="Q81" s="66">
+        <v>41.13</v>
+      </c>
+      <c r="R81" s="66">
+        <v>49.47</v>
+      </c>
+      <c r="S81" s="66">
+        <v>58.23</v>
+      </c>
+      <c r="T81" s="66">
+        <v>66.78</v>
+      </c>
+      <c r="U81" s="66">
+        <v>75.22</v>
+      </c>
+      <c r="V81" s="66">
+        <v>83.75</v>
+      </c>
+    </row>
+    <row r="82" spans="6:24" ht="13.9" x14ac:dyDescent="0.4">
+      <c r="F82" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="G82" s="1"/>
+      <c r="H82" s="11">
+        <v>50</v>
+      </c>
+      <c r="I82" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K82" s="63" t="s">
+        <v>73</v>
+      </c>
+      <c r="M82" s="13">
+        <f t="shared" ref="M82:V82" si="4">M81/$M79*100</f>
+        <v>7.913165266106442</v>
+      </c>
+      <c r="N82" s="62">
+        <f t="shared" si="4"/>
+        <v>17.880485527544348</v>
+      </c>
+      <c r="O82" s="62">
+        <f t="shared" si="4"/>
+        <v>27.87114845938375</v>
+      </c>
+      <c r="P82" s="62">
+        <f t="shared" si="4"/>
+        <v>37.955182072829132</v>
+      </c>
+      <c r="Q82" s="62">
+        <f t="shared" si="4"/>
+        <v>48.004201680672267</v>
+      </c>
+      <c r="R82" s="62">
+        <f t="shared" si="4"/>
+        <v>57.738095238095234</v>
+      </c>
+      <c r="S82" s="62">
+        <f t="shared" si="4"/>
+        <v>67.962184873949568</v>
+      </c>
+      <c r="T82" s="62">
+        <f t="shared" si="4"/>
+        <v>77.941176470588232</v>
+      </c>
+      <c r="U82" s="62">
+        <f t="shared" si="4"/>
+        <v>87.791783380018657</v>
+      </c>
+      <c r="V82" s="62">
+        <f t="shared" si="4"/>
+        <v>97.747432306255831</v>
+      </c>
+      <c r="W82" s="61"/>
+    </row>
+    <row r="83" spans="6:24" ht="13.9" x14ac:dyDescent="0.4">
+      <c r="F83" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="G83" s="1"/>
+      <c r="H83" s="11">
+        <f>H81+H82</f>
+        <v>70</v>
+      </c>
+      <c r="I83" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="K83" s="63" t="s">
+        <v>82</v>
+      </c>
+      <c r="M83" s="66">
+        <v>10</v>
+      </c>
+      <c r="N83" s="66">
+        <v>20</v>
+      </c>
+      <c r="O83" s="66">
+        <v>30</v>
+      </c>
+      <c r="P83" s="66">
+        <v>40</v>
+      </c>
+      <c r="Q83" s="66">
+        <v>50</v>
+      </c>
+      <c r="R83" s="66">
+        <v>60</v>
+      </c>
+      <c r="S83" s="66">
+        <v>70</v>
+      </c>
+      <c r="T83" s="66">
+        <v>80</v>
+      </c>
+      <c r="U83" s="66">
+        <v>90</v>
+      </c>
+      <c r="V83" s="66">
+        <v>100</v>
+      </c>
+      <c r="W83" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="X83" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="84" spans="6:24" ht="13.9" x14ac:dyDescent="0.4">
+      <c r="F84" s="51" t="s">
+        <v>63</v>
+      </c>
+      <c r="G84" s="1"/>
+      <c r="H84" s="29">
+        <v>27.6</v>
+      </c>
+      <c r="I84" s="52" t="s">
+        <v>64</v>
+      </c>
+      <c r="K84" s="63" t="s">
+        <v>74</v>
+      </c>
+      <c r="M84" s="62">
+        <f t="shared" ref="M84" si="5">M82-M83</f>
+        <v>-2.086834733893558</v>
+      </c>
+      <c r="N84" s="62">
+        <f>N82-N83</f>
+        <v>-2.1195144724556521</v>
+      </c>
+      <c r="O84" s="62">
+        <f t="shared" ref="O84:V84" si="6">O82-O83</f>
+        <v>-2.1288515406162496</v>
+      </c>
+      <c r="P84" s="62">
+        <f t="shared" si="6"/>
+        <v>-2.0448179271708682</v>
+      </c>
+      <c r="Q84" s="62">
+        <f t="shared" si="6"/>
+        <v>-1.9957983193277329</v>
+      </c>
+      <c r="R84" s="62">
+        <f t="shared" si="6"/>
+        <v>-2.2619047619047663</v>
+      </c>
+      <c r="S84" s="62">
+        <f t="shared" si="6"/>
+        <v>-2.0378151260504325</v>
+      </c>
+      <c r="T84" s="62">
+        <f t="shared" si="6"/>
+        <v>-2.058823529411768</v>
+      </c>
+      <c r="U84" s="62">
+        <f t="shared" si="6"/>
+        <v>-2.2082166199813429</v>
+      </c>
+      <c r="V84" s="62">
+        <f t="shared" si="6"/>
+        <v>-2.2525676937441688</v>
+      </c>
+      <c r="W84" s="62">
+        <f>STDEV(M84:V84)</f>
+        <v>9.3240909921851828E-2</v>
+      </c>
+      <c r="X84" s="62">
+        <f>AVERAGE(M84:V84)</f>
+        <v>-2.1195144724556538</v>
+      </c>
+    </row>
+    <row r="85" spans="6:24" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="F85" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="G85" s="1"/>
+      <c r="H85" s="29">
+        <f>H80-H84</f>
+        <v>-27.6</v>
+      </c>
+      <c r="I85" s="52"/>
+    </row>
+    <row r="86" spans="6:24" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="F86" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="G86" s="42"/>
+      <c r="H86" s="43" t="e">
+        <f>H85/(H80/100)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I86" s="52"/>
+    </row>
+    <row r="87" spans="6:24" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="F87" s="51"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="11"/>
+      <c r="I87" s="52"/>
+    </row>
+    <row r="88" spans="6:24" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="F88" s="54" t="s">
+        <v>68</v>
+      </c>
+      <c r="G88" s="55"/>
+      <c r="H88" s="56" t="e">
+        <f>H86/H83-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I88" s="57"/>
+    </row>
+    <row r="124" spans="11:24" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="K124" s="63" t="s">
+        <v>72</v>
+      </c>
+      <c r="L124" t="s">
+        <v>83</v>
+      </c>
+      <c r="M124" s="24">
+        <v>85.68</v>
+      </c>
+    </row>
+    <row r="125" spans="11:24" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="K125" s="63" t="s">
+        <v>61</v>
+      </c>
+      <c r="M125" s="21">
+        <v>1</v>
+      </c>
+      <c r="N125" s="6">
+        <v>2</v>
+      </c>
+      <c r="O125" s="6">
+        <v>3</v>
+      </c>
+      <c r="P125" s="21">
+        <v>4</v>
+      </c>
+      <c r="Q125" s="21">
+        <v>5</v>
+      </c>
+      <c r="R125" s="21">
+        <v>6</v>
+      </c>
+      <c r="S125" s="21">
+        <v>7</v>
+      </c>
+      <c r="T125" s="21">
+        <v>8</v>
+      </c>
+      <c r="U125" s="21">
+        <v>9</v>
+      </c>
+      <c r="V125" s="21">
+        <v>10</v>
+      </c>
+      <c r="W125" s="24"/>
+    </row>
+    <row r="126" spans="11:24" ht="13.9" x14ac:dyDescent="0.4">
+      <c r="K126" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="M126" s="64">
+        <v>8.24</v>
+      </c>
+      <c r="N126" s="65">
+        <v>8.15</v>
+      </c>
+      <c r="O126" s="66">
+        <v>8.2100000000000009</v>
+      </c>
+      <c r="P126" s="66">
+        <f>16.38-8.21</f>
+        <v>8.1699999999999982</v>
+      </c>
+      <c r="Q126" s="66">
+        <v>8.16</v>
+      </c>
+      <c r="R126" s="66">
+        <v>8.11</v>
+      </c>
+      <c r="S126" s="66"/>
+      <c r="T126" s="66"/>
+      <c r="U126" s="66"/>
+      <c r="V126" s="66"/>
+    </row>
+    <row r="127" spans="11:24" ht="13.9" x14ac:dyDescent="0.4">
+      <c r="K127" s="63" t="s">
+        <v>73</v>
+      </c>
+      <c r="M127" s="13">
+        <f t="shared" ref="M127:R127" si="7">M126/$M124*100</f>
+        <v>9.6171802054154991</v>
+      </c>
+      <c r="N127" s="62">
+        <f t="shared" si="7"/>
+        <v>9.5121381886087768</v>
+      </c>
+      <c r="O127" s="62">
+        <f t="shared" si="7"/>
+        <v>9.5821661998132601</v>
+      </c>
+      <c r="P127" s="62">
+        <f t="shared" si="7"/>
+        <v>9.5354808590102671</v>
+      </c>
+      <c r="Q127" s="62">
+        <f t="shared" si="7"/>
+        <v>9.5238095238095237</v>
+      </c>
+      <c r="R127" s="62">
+        <f t="shared" si="7"/>
+        <v>9.4654528478057873</v>
+      </c>
+      <c r="S127" s="62"/>
+      <c r="T127" s="62"/>
+      <c r="U127" s="62"/>
+      <c r="V127" s="62"/>
+      <c r="W127" s="61"/>
+    </row>
+    <row r="128" spans="11:24" ht="13.9" x14ac:dyDescent="0.4">
+      <c r="K128" s="63" t="s">
+        <v>82</v>
+      </c>
+      <c r="M128" s="66">
+        <v>10</v>
+      </c>
+      <c r="N128" s="66">
+        <v>10</v>
+      </c>
+      <c r="O128" s="66">
+        <v>10</v>
+      </c>
+      <c r="P128" s="66">
+        <v>10</v>
+      </c>
+      <c r="Q128" s="66">
+        <v>10</v>
+      </c>
+      <c r="R128" s="66">
+        <v>10</v>
+      </c>
+      <c r="S128" s="66"/>
+      <c r="T128" s="66"/>
+      <c r="U128" s="66"/>
+      <c r="V128" s="66"/>
+      <c r="W128" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="X128" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="129" spans="11:24" ht="13.9" x14ac:dyDescent="0.4">
+      <c r="K129" s="63" t="s">
+        <v>74</v>
+      </c>
+      <c r="M129" s="62">
+        <f t="shared" ref="M129" si="8">M127-M128</f>
+        <v>-0.38281979458450088</v>
+      </c>
+      <c r="N129" s="62">
+        <f>N127-N128</f>
+        <v>-0.4878618113912232</v>
+      </c>
+      <c r="O129" s="62">
+        <f t="shared" ref="O129" si="9">O127-O128</f>
+        <v>-0.41783380018673988</v>
+      </c>
+      <c r="P129" s="62">
+        <f t="shared" ref="P129" si="10">P127-P128</f>
+        <v>-0.4645191409897329</v>
+      </c>
+      <c r="Q129" s="62">
+        <f t="shared" ref="Q129" si="11">Q127-Q128</f>
+        <v>-0.47619047619047628</v>
+      </c>
+      <c r="R129" s="62">
+        <f t="shared" ref="R129" si="12">R127-R128</f>
+        <v>-0.53454715219421267</v>
+      </c>
+      <c r="S129" s="62"/>
+      <c r="T129" s="62"/>
+      <c r="U129" s="62"/>
+      <c r="V129" s="62"/>
+      <c r="W129" s="62">
+        <f>STDEV(M129:V129)</f>
+        <v>5.3569606218670039E-2</v>
+      </c>
+      <c r="X129" s="62">
+        <f>AVERAGE(M129:V129)</f>
+        <v>-0.4606286959228143</v>
+      </c>
+    </row>
+    <row r="131" spans="11:24" x14ac:dyDescent="0.35">
+      <c r="M131" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="133" spans="11:24" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="K133" s="63" t="s">
+        <v>72</v>
+      </c>
+      <c r="L133" t="s">
+        <v>83</v>
+      </c>
+      <c r="M133" s="24">
+        <v>85.68</v>
+      </c>
+    </row>
+    <row r="134" spans="11:24" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="K134" s="63" t="s">
+        <v>61</v>
+      </c>
+      <c r="M134" s="21">
+        <v>1</v>
+      </c>
+      <c r="N134" s="6">
+        <v>2</v>
+      </c>
+      <c r="O134" s="6">
+        <v>3</v>
+      </c>
+      <c r="P134" s="21">
+        <v>4</v>
+      </c>
+      <c r="Q134" s="21">
+        <v>5</v>
+      </c>
+      <c r="R134" s="21">
+        <v>6</v>
+      </c>
+      <c r="S134" s="21">
+        <v>7</v>
+      </c>
+      <c r="T134" s="21">
+        <v>8</v>
+      </c>
+      <c r="U134" s="21">
+        <v>9</v>
+      </c>
+      <c r="V134" s="21">
+        <v>10</v>
+      </c>
+      <c r="W134" s="24"/>
+    </row>
+    <row r="135" spans="11:24" ht="13.9" x14ac:dyDescent="0.4">
+      <c r="K135" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="M135" s="64">
+        <v>8.5</v>
+      </c>
+      <c r="N135" s="65">
+        <v>17.13</v>
+      </c>
+      <c r="O135" s="66">
+        <v>25.65</v>
+      </c>
+      <c r="P135" s="66">
+        <v>34.26</v>
+      </c>
+      <c r="Q135" s="66">
+        <v>42.79</v>
+      </c>
+      <c r="R135" s="66">
+        <v>51.38</v>
+      </c>
+      <c r="S135" s="66">
+        <v>59.91</v>
+      </c>
+      <c r="T135" s="66">
+        <v>68.47</v>
+      </c>
+      <c r="U135" s="66">
+        <v>77</v>
+      </c>
+      <c r="V135" s="66">
+        <v>85.59</v>
+      </c>
+    </row>
+    <row r="136" spans="11:24" ht="13.9" x14ac:dyDescent="0.4">
+      <c r="K136" s="63" t="s">
+        <v>73</v>
+      </c>
+      <c r="M136" s="13">
+        <f t="shared" ref="M136:V136" si="13">M135/$M133*100</f>
+        <v>9.9206349206349209</v>
+      </c>
+      <c r="N136" s="62">
+        <f t="shared" si="13"/>
+        <v>19.99299719887955</v>
+      </c>
+      <c r="O136" s="62">
+        <f t="shared" si="13"/>
+        <v>29.936974789915961</v>
+      </c>
+      <c r="P136" s="62">
+        <f t="shared" si="13"/>
+        <v>39.9859943977591</v>
+      </c>
+      <c r="Q136" s="62">
+        <f t="shared" si="13"/>
+        <v>49.94164332399626</v>
+      </c>
+      <c r="R136" s="62">
+        <f t="shared" si="13"/>
+        <v>59.967320261437905</v>
+      </c>
+      <c r="S136" s="62">
+        <f t="shared" si="13"/>
+        <v>69.922969187675065</v>
+      </c>
+      <c r="T136" s="62">
+        <f t="shared" si="13"/>
+        <v>79.91363211951446</v>
+      </c>
+      <c r="U136" s="62">
+        <f t="shared" si="13"/>
+        <v>89.86928104575162</v>
+      </c>
+      <c r="V136" s="62">
+        <f t="shared" si="13"/>
+        <v>99.894957983193279</v>
+      </c>
+      <c r="W136" s="61"/>
+    </row>
+    <row r="137" spans="11:24" ht="13.9" x14ac:dyDescent="0.4">
+      <c r="K137" s="63" t="s">
+        <v>82</v>
+      </c>
+      <c r="M137" s="66">
+        <v>10</v>
+      </c>
+      <c r="N137" s="66">
+        <v>20</v>
+      </c>
+      <c r="O137" s="66">
+        <v>30</v>
+      </c>
+      <c r="P137" s="66">
+        <v>40</v>
+      </c>
+      <c r="Q137" s="66">
+        <v>50</v>
+      </c>
+      <c r="R137" s="66">
+        <v>60</v>
+      </c>
+      <c r="S137" s="66">
+        <v>70</v>
+      </c>
+      <c r="T137" s="66">
+        <v>80</v>
+      </c>
+      <c r="U137" s="66">
+        <v>90</v>
+      </c>
+      <c r="V137" s="66">
+        <v>100</v>
+      </c>
+      <c r="W137" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="X137" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="138" spans="11:24" ht="13.9" x14ac:dyDescent="0.4">
+      <c r="K138" s="63" t="s">
+        <v>74</v>
+      </c>
+      <c r="M138" s="62">
+        <f t="shared" ref="M138" si="14">M136-M137</f>
+        <v>-7.9365079365079083E-2</v>
+      </c>
+      <c r="N138" s="62">
+        <f>N136-N137</f>
+        <v>-7.0028011204499307E-3</v>
+      </c>
+      <c r="O138" s="62">
+        <f t="shared" ref="O138" si="15">O136-O137</f>
+        <v>-6.3025210084038719E-2</v>
+      </c>
+      <c r="P138" s="62">
+        <f t="shared" ref="P138" si="16">P136-P137</f>
+        <v>-1.4005602240899861E-2</v>
+      </c>
+      <c r="Q138" s="62">
+        <f t="shared" ref="Q138" si="17">Q136-Q137</f>
+        <v>-5.8356676003739949E-2</v>
+      </c>
+      <c r="R138" s="62">
+        <f t="shared" ref="R138" si="18">R136-R137</f>
+        <v>-3.267973856209494E-2</v>
+      </c>
+      <c r="S138" s="62">
+        <f t="shared" ref="S138" si="19">S136-S137</f>
+        <v>-7.7030812324935027E-2</v>
+      </c>
+      <c r="T138" s="62">
+        <f t="shared" ref="T138" si="20">T136-T137</f>
+        <v>-8.6367880485539672E-2</v>
+      </c>
+      <c r="U138" s="62">
+        <f t="shared" ref="U138" si="21">U136-U137</f>
+        <v>-0.13071895424837976</v>
+      </c>
+      <c r="V138" s="62">
+        <f t="shared" ref="V138" si="22">V136-V137</f>
+        <v>-0.10504201680672054</v>
+      </c>
+      <c r="W138" s="62">
+        <f>STDEV(M138:V138)</f>
+        <v>3.9137181263491784E-2</v>
+      </c>
+      <c r="X138" s="62">
+        <f>AVERAGE(M138:V138)</f>
+        <v>-6.5359477124187743E-2</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
